--- a/erp-server/erp-server-file/src/main/resources/excel/tms/shippingCalculation_first.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/shippingCalculation_first.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>物流商</t>
   </si>
@@ -28,6 +41,9 @@
     <t>有效期</t>
   </si>
   <si>
+    <t>时效</t>
+  </si>
+  <si>
     <t>币别</t>
   </si>
   <si>
@@ -56,6 +72,9 @@
   </si>
   <si>
     <t>{.effectivePeriod}</t>
+  </si>
+  <si>
+    <t>{.effectiveTimeStr}</t>
   </si>
   <si>
     <t>{.currency}</t>
@@ -79,7 +98,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1007,22 +1026,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="19.125" customWidth="1"/>
     <col min="3" max="3" width="22.375" customWidth="1"/>
-    <col min="4" max="4" width="21.125" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="16.375" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="18.75" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="19.875" customWidth="1"/>
+    <col min="4" max="5" width="21.125" customWidth="1"/>
+    <col min="6" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="21" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,37 +1072,43 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
